--- a/04_DESIGN_TABLES/DesignTable_6504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1019,12 +1024,17 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>Air-Way s100 only (double-pass 14 rows)</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L13@DRIVE=2.33~2.330; CHEX@HEX=1.13~1.125; C3HEX@HEX=1.25~1.250; D1@BORE=0.61~0.609; D2@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1445,24 +1455,58 @@
           <t>6504-04-06</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1/4-3/8</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>6504-04-06</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>7/16-20 (B (1) UN/UNF-2A) x 9/16-18 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1986 Overall Length = 1.590 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'L5 LGTH' = 1.590 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1986 Hex Flat = 0.562 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'C HEX' = 0.562 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1986 Nut Hex 1 = 0.688 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'C1 HEX' = 0.688 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1986 Side 1 ID = 0.172 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'B1 DRILL' = 0.172 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1986 Side 2 ID = 0.297 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'B2 DRILL' = 0.297 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-04-06 column 'L LGTH' = 1.210 (catalog_verified.json); OMi Items!P1986 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.380; THDMAJ_B1@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1986 "7/16-20 UNF"; catalog B1 7/16-20; THDMAJ_B2@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1986 "9/16-18 UNF"; catalog B2 9/16-18; $PRP@TubeOD: OMi Items!T1986 Side 1 Size " 1/4 " + Items!Z1986 Side 2 Size " 3/8 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[6] thread texts, format of the built 6504 rows</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.380 vs Brennan-measured swivel -06 NOSETIP_B 0.38 (gen_straight2 SWIV_MEAS); nut hex OMi 0.688 vs SWIV_MEAS AF 0.6875</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1473,6 +1517,11 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>6504-04-06</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1482,24 +1531,58 @@
           <t>6504-06-04</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3/8-1/4</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>6504-06-04</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>9/16-18 (B (1) UN/UNF-2A) x 7/16-20 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1987 Overall Length = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'L5 LGTH' = 1.504 (catalog_verified.json): rounding only; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1987 Hex Flat = 0.625 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'C HEX' = 0.625 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1987 Nut Hex 1 = 0.562 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'C1 HEX' = 0.563 (catalog_verified.json): rounding only; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1987 Side 1 ID = 0.297 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'B1 DRILL' = 0.297 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1987 Side 2 ID = 0.172 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'B2 DRILL' = 0.172 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-06-04 column 'L LGTH' = 1.160 (catalog_verified.json); OMi Items!P1987 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.340; THDMAJ_B1@DRIVE: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1987 "9/16-18 UNF"; catalog B1 9/16-18; THDMAJ_B2@DRIVE: gen_straight2 JIC[4] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1987 "7/16-20 UNF"; catalog B2 7/16-20; $PRP@TubeOD: OMi Items!T1987 Side 1 Size " 3/8 " + Items!Z1987 Side 2 Size " 1/4 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[6] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[4] thread texts, format of the built 6504 rows</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.340 vs Brennan-measured swivel -04 NOSETIP_B 0.35 (gen_straight2 SWIV_MEAS); nut hex OMi 0.562 vs SWIV_MEAS AF 0.5625</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1510,6 +1593,11 @@
       <c r="Q18" t="inlineStr">
         <is>
           <t>6504-06-04</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1519,24 +1607,58 @@
           <t>6504-08-10</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>1/2-5/8</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>6504-08-10</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>3/4-16 (B (1) UN/UNF-2A) x 7/8-14 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1992 Overall Length = 2.070 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'L5 LGTH' = 2.070 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1992 Hex Flat = 0.938 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'C HEX' = 0.938 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V1992 Nut Hex 1 = 1.000 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'C1 HEX' = 1.000 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1992 Side 1 ID = 0.391 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'B1 DRILL' = 0.391 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1992 Side 2 ID = 0.484 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'B2 DRILL' = 0.484 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-08-10 column 'L LGTH' = 1.570 (catalog_verified.json); OMi Items!P1992 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.500; THDMAJ_B1@DRIVE: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U1992 "3/4-16 UNF"; catalog B1 3/4-16; THDMAJ_B2@DRIVE: gen_straight2 JIC[10] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA1992 "7/8-14 UNF"; catalog B2 7/8-14; $PRP@TubeOD: OMi Items!T1992 Side 1 Size " 1/2 " + Items!Z1992 Side 2 Size " 5/8 " (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[8] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[10] thread texts, format of the built 6504 rows</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.500 vs Brennan-measured swivel -10 NOSETIP_B 0.5 (gen_straight2 SWIV_MEAS); nut hex OMi 1.0 vs SWIV_MEAS AF 1.0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1547,6 +1669,11 @@
       <c r="Q19" t="inlineStr">
         <is>
           <t>6504-08-10</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1704,24 +1831,58 @@
           <t>6504-12-16</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>3/4-1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>6504-12-16</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (B (1) UN/UNF-2A) x 1 5/16-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L13@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L2000 Overall Length = 2.450 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L5 LGTH' = 2.450 (catalog_verified.json): equal; CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R2000 Hex Flat = 1.375 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C HEX' = 1.375 (catalog_verified.json): equal; C3HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!V2000 Nut Hex 1 = 1.500 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'C1 HEX' = 1.500 (catalog_verified.json): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2000 Side 1 ID = 0.609 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B1 DRILL' = 0.609 (catalog_verified.json): equal; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X2000 Side 2 ID = 0.844 (OMi first, user 2026-09-25); cross-check Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'B2 DRILL' = 0.844 (catalog_verified.json): equal; L14@DRIVE: Brennan TFA catalog p17 table TFA-p017-t05 (MJ-FJS STRAIGHT) row 6504-12-16 column 'L LGTH' = 1.860 (catalog_verified.json); OMi Items!P2000 L 1 blank, no Air-Way row; pairs with OMi L13 = catalog L5 (same manufacturer); nut face to nose L13 - L14 = 0.590; THDMAJ_B1@DRIVE: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, male JIC end (first dash); OMi Items!U2000 "1-1/16-12 UN"; catalog B1 1-1/16-12; THDMAJ_B2@DRIVE: gen_straight2 JIC[16] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) thread major, swivel end (second dash); OMi Items!AA2000 "1-5/16-12 UN"; catalog B2 1-5/16-12; $PRP@TubeOD: OMi Items!T2000 Side 1 Size " 3/4 " + Items!Z2000 Side 2 Size "1" (format of the built 6504 rows: first-second); $PRP@Threads: gen_straight2 JIC[12] (tools_new/generators/templates/DesignTable_2403_SW2.xlsx: MS33656J chain, VERIFIED vs Brennan) / JIC[16] thread texts, format of the built 6504 rows</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | BRENNAN-ONLY (2026-10-18) for L14 (male tip to seat) only - every other size is OMi's; nut face to nose L13 - L14 = 0.590 vs Brennan-measured swivel -16 NOSETIP_B 0.6 (gen_straight2 SWIV_MEAS); nut hex OMi 1.5 vs SWIV_MEAS AF 1.5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -1732,6 +1893,11 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>6504-12-16</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -655,7 +655,7 @@
         <v>1.23</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="E5" t="n">
         <v>0.88</v>
@@ -694,12 +694,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped)</t>
+          <t>Air-Way s100 only (double-pass 14 rows); CHEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1989 Hex Flat = 0.813 (table had 0.75) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1989 Side 1 ID = 0.297 (table had empty: Air-Way garbled ".030") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D2@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1989 Side 2 ID = 0.391 (table had empty: Air-Way garbled ".039") [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] - batch 15, 2026-10-02 (staged, not shipped); CHEX@HEX: Air-Way 0.75 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision</t>
+          <t>D (1)/D (2) printed ".030"/".039" on Air-Way (garbled 0.30/0.39); copied as printed | D (1): printed ".030" (not a clean decimal) -&gt; left empty, MISSING | D (2): printed ".039" (not a clean decimal) -&gt; left empty, MISSING | batch 15, 2026-10-02 (staged, not shipped): D (1) / D (2) filled from OMi Items!S1989 / X1989 (0.297 / 0.391; = Brennan TFA p17 B1 / B2 DRILL, same source; Air-Way's garbled .030 / .039 read as 0.30 / 0.39 agree after rounding) -&gt; MISSING to ASSUMED. NOT changed: L13 stays Air-Way 1.65 although OMi Overall Length Items!L1989 = 1.730 is the same feature (Brennan TFA p17 drawing letter L5 = male tip to nut face, Q-B-OTHER-6504): OMi gives no L14, and OMi 1.730 with Air-Way L14 1.23 would put the swivel nose 0.50 from the nut face (Air-Way 0.42, Brennan 6500-08 STEP 0.43, catalog L5 - L 0.41); the consistent Brennan pair 1.730 / 1.32 needs the catalog L 1.32 in OMi's place (Q-NEW-CATRANK / Q-BRENNAN-ONLY) - user decision | 2026-10-20 Air-Way first: CHEX@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.75</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>[BRENNAN-CELL 2026-10-20: D1@BORE] Air-Way s100 only (double-pass 14 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S2006 Side 1 ID = 1.312 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Brennan TFA catalog p17 table TFA-p017-t05 "MJ-FJS STRAIGHT" row 6504-24-24 col "B1 DRILL" = 1.312 [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan]</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed</t>
+          <t>D (1) printed 1.38 (D (2) 1.31); copied as printed | 2026-10-20 D1@BORE = Brennan 1.312 (Air-Way 1.38 cannot be built: Air-Way bore 1.38 &gt;= the -24 JIC tip dia 1.381 (generator BLOCKED))</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1446,6 +1446,11 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>6504-24-24</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_6504.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6504.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1688,24 +1688,58 @@
           <t>6504-08-12</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1/2-3/4</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>6504-08-12</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3/4-16 (B (1) UN/UNF-2A) x 1 1/16-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1993; L14 = L13 - 0.57 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[12] NOSETIP_B, Brennan-measured; Air-Way prints 0.56 / 0.57) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1993; L14 = L13 - 0.57 (A12, end-library offset; Air-Way 0.56 / 0.57); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1716,6 +1750,11 @@
       <c r="Q20" t="inlineStr">
         <is>
           <t>6504-08-12</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1725,24 +1764,58 @@
           <t>6504-10-08</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5/8-1/2</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>6504-10-08</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>7/8-14 (B (1) UN/UNF-2A) x 3/4-16 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1994; L14 = L13 - 0.43 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[8] NOSETIP_B, Brennan-measured; Air-Way prints 0.42) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1994; L14 = L13 - 0.43 (A12, end-library offset; Air-Way 0.42); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1753,6 +1826,11 @@
       <c r="Q21" t="inlineStr">
         <is>
           <t>6504-10-08</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1762,24 +1840,58 @@
           <t>6504-10-12</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5/8-3/4</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>6504-10-12</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>7/8-14 (B (1) UN/UNF-2A) x 1 1/16-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1996; L14 = L13 - 0.57 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[12] NOSETIP_B, Brennan-measured; Air-Way prints 0.56 / 0.57) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1996; L14 = L13 - 0.57 (A12, end-library offset; Air-Way 0.56 / 0.57); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1790,6 +1902,11 @@
       <c r="Q22" t="inlineStr">
         <is>
           <t>6504-10-12</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1799,24 +1916,58 @@
           <t>6504-12-10</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3/4-5/8</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>6504-12-10</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (B (1) UN/UNF-2A) x 7/8-14 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 1998; L14 = L13 - 0.50 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[10] NOSETIP_B, Brennan-measured; Air-Way prints 0.49 / 0.50) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 1998; L14 = L13 - 0.50 (A12, end-library offset; Air-Way 0.49 / 0.50); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -1827,6 +1978,11 @@
       <c r="Q23" t="inlineStr">
         <is>
           <t>6504-12-10</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1912,24 +2068,58 @@
           <t>6504-16-20</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.687</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.078</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1-1 1/4</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>6504-16-20</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (B (1) UN/UNF-2A) x 1 5/8-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 2003; L14 = L13 - 0.64 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[20] NOSETIP_B, Brennan-measured; Air-Way prints 0.62 / 0.63) [ASSUMPTION logged]; thread majors from the end library; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 2003; L14 = L13 - 0.64 (A12, end-library offset; Air-Way 0.62 / 0.63); not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -1940,6 +2130,11 @@
       <c r="Q25" t="inlineStr">
         <is>
           <t>6504-16-20</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
@@ -1949,24 +2144,58 @@
           <t>6504-32-32</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>6504-32-32</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (B (1) UN/UNF-2A) x 2 1/2-12 (B (2) UN/UNF-2B)</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L13 / hex / nut hex / bores = OMi WebsitePartsInfo2026.xlsx Items row 2007; L14 = L13 - 0.95 (A12: swivel offset = the end library's per-size value, SWIV_MEAS[32] NOSETIP_B, Brennan-measured; Air-Way prints 0.94 (6505-32-32 only)) [ASSUMPTION logged]; thread majors from the end library; Brennan TFA p17 6504-32-32 prints L 3.700 / L5 2.862 (inconsistent: seat beyond the nut face; Q-CAT-6504-32-32-L) - not used; OMi 3.800 kept by the source order, and OMi L13 - the library offset = 2.85 = the catalog's 2.862 within 0.012; hex 2.625 / nut 2.875 / drills 1.781 equal</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): OMi Items row 2007; L14 = L13 - 0.95 (A12, end-library offset; Air-Way 0.94 (6505-32-32 only)); Brennan TFA p17 6504-32-32 prints L 3.700 / L5 2.862 (inconsistent: seat beyond the nut face; Q-CAT-6504-32-32-L) - not used; OMi 3.800 kept by the source order, and OMi L13 - the library offset = 2.85 = the catalog's 2.862 within 0.012; hex 2.625 / nut 2.875 / drills 1.781 equal</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -1977,6 +2206,11 @@
       <c r="Q26" t="inlineStr">
         <is>
           <t>6504-32-32</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>OMI</t>
         </is>
       </c>
     </row>
